--- a/data/trans_orig/IP07C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24900</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>33030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43578</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>63597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>54968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72693</t>
+          <t>72006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>64819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82372</t>
+          <t>82115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>125438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150077</t>
+          <t>149152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,82 +1429,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7993</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8577</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92302</t>
+          <t>91884</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32409</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68023</t>
+          <t>66571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94513</t>
+          <t>91557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86568</t>
+          <t>86575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106902</t>
+          <t>108241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85520</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106762</t>
+          <t>106351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177811</t>
+          <t>176030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208128</t>
+          <t>207527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>63703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73831</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129499</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78170</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>116514</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>149897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146177</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>182999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>311585</t>
+          <t>309451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348669</t>
+          <t>348953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53346</t>
+          <t>53388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34334</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>49377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73449</t>
+          <t>73653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71003</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90329</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>71217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90783</t>
+          <t>91514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147399</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175691</t>
+          <t>176848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34980</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>54013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54251</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75565</t>
+          <t>76199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103098</t>
+          <t>102372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>45286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75585</t>
+          <t>73901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61836</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83568</t>
+          <t>82638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81227</t>
+          <t>80588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101838</t>
+          <t>102779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149131</t>
+          <t>150148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178997</t>
+          <t>178254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>82407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71698</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136530</t>
+          <t>135655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171172</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107808</t>
+          <t>108704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>137310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167613</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158383</t>
+          <t>156454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>187922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304901</t>
+          <t>303096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343086</t>
+          <t>345763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>47977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>35084</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>47956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53605</t>
+          <t>53775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96386</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80736</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>103798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86953</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109455</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173784</t>
+          <t>173984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205801</t>
+          <t>206065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46582</t>
+          <t>45920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>31862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50560</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65907</t>
+          <t>65637</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90805</t>
+          <t>91177</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>55625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>43061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64789</t>
+          <t>65065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84874</t>
+          <t>84630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112955</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59434</t>
+          <t>57678</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>80881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122238</t>
+          <t>122899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151971</t>
+          <t>152229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125396</t>
+          <t>124252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162309</t>
+          <t>158861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83930</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160324</t>
+          <t>161242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202573</t>
+          <t>203389</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143463</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174969</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151372</t>
+          <t>151390</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182659</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305095</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>351863</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,84 +722,84 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2681</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>685</t>
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6563</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2550</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6067</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6298</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6134</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17944</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12607</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24465</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16567</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11103</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23149</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11175</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>23399</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14,83%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17944</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12017</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24736</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24883</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18384</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>28389</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21423</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36421</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21322</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36084</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24883</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>33030</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63597</t>
+          <t>63946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74003</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66180</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81976</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54968</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72006</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>55853</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72938</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74003</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>64819</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125438</t>
+          <t>124827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149152</t>
+          <t>149524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>121657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>121657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>121657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>121657</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>121657</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121657</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2057</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5763</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5097</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4049</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5785</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4775</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9462</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9371</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5595</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44010</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34579</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53700</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>34864</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26437</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>44296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>26438</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>43952</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>14,95%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>44010</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34670</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53330</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66499</t>
+          <t>66869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91884</t>
+          <t>92751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40787</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32756</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>50053</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>38321</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29605</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47100</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29968</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>47171</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40787</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32145</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49755</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66571</t>
+          <t>67624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91557</t>
+          <t>91785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>95524</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84614</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106291</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>96855</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86575</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108241</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>107959</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>54,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>95524</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>85092</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>106351</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176030</t>
+          <t>177934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207527</t>
+          <t>206881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>183761</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>183761</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>183761</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>176872</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>176872</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>176872</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>183761</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>183761</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>183761</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8542</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2057</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5836</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5535</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8240</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8323</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7325</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3903</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12654</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3927</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12787</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4240</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8837</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>61954</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>50686</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73237</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16,6%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>51431</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>42176</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63703</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>41494</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62229</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>17,82%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>61954</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51571</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>74238</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99722</t>
+          <t>99324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129499</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>65670</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>54762</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>78459</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>66710</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>55687</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>78536</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>55590</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>78496</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>23,12%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>65670</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>77124</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116514</t>
+          <t>116461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149897</t>
+          <t>148379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -2538,74 +2538,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>169526</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>155171</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>183024</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55,51%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>50,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>59,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>161059</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>146234</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>174610</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>146263</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>174622</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>55,81%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>50,68%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>60,51%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>169526</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>155494</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>182999</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>55,51%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>491</t>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309451</t>
+          <t>312227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348953</t>
+          <t>348844</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>305417</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>305417</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>305417</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>429</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>288583</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>288583</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>288583</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>305417</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>305417</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>305417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,107 +2998,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7307</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6976</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3856</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3856</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8717</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5097</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10420</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6997</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11561</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3512</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12652</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5097</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9611</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40201</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31322</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50253</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24751</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17771</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33078</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18133</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>33350</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40201</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>31180</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50409</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53388</t>
+          <t>54483</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77079</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26282</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19237</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34250</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>34405</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>26707</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>43744</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>27147</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>44215</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26282</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19785</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34716</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81334</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70011</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91990</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80508</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70237</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89730</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71286</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>90797</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>81334</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71217</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91514</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>52,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>148438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176848</t>
+          <t>175933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154145</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154145</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154145</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149285</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149285</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154145</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154145</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154145</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4236</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9275</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8990</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2936</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11132</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4843</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9948</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11293</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44195</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35093</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54285</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26,1%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>44524</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>34856</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>54013</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>35600</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54995</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>44195</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34517</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53779</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>75955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>101894</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26802</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20252</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34735</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35821</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27766</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>45286</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28451</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46143</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>26802</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19721</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34708</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51540</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73901</t>
+          <t>75931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91384</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80345</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100745</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>72018</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61396</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>82638</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>61792</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>82096</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>44,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91384</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80588</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102779</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150148</t>
+          <t>148588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178254</t>
+          <t>177234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161441</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161441</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161441</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169313</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169313</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1954</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6859</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12682</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5339</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11307</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6471</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17822</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>11840</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7120</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6685</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>18156</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11307</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6648</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>18063</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>84396</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>71821</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>97272</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>69275</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>58491</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>82407</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>57484</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>82853</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>22,29%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>84396</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>70082</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>97009</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>26,09%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135655</t>
+          <t>134383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>169552</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>53083</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42728</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>63826</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>70226</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>59393</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>82888</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>58343</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>83429</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>22,6%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>53083</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>41573</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>64009</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108704</t>
+          <t>108636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140572</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>172718</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>158074</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>186310</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>152525</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>137310</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>166502</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>137301</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>166425</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>49,09%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>44,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>53,58%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>172718</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>156454</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>187922</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303096</t>
+          <t>304765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345763</t>
+          <t>346803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>323458</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>323458</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>323458</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310726</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310726</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310726</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>323458</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>323458</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>323458</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8236</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1916</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5105</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3637</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8183</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11660</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8208</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4280</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13053</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4597</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14405</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6301</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11188</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26399</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18821</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35156</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>37774</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29733</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47977</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>28813</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47649</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>21,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26399</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19458</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35084</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77258</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43630</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34444</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53557</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>39125</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30248</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47956</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30237</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48018</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>43630</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35431</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53775</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70019</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>96633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98644</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>91626</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81098</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103798</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80280</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101898</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>51,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>98644</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87359</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109674</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173984</t>
+          <t>174898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206065</t>
+          <t>206380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>178649</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>178649</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>178649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,74 +5956,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2432</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6963</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6960</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12034</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11013</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17923</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6359</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17119</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>6,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6896</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3437</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>25314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41210</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32533</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51956</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,16%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36650</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28373</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>45920</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27333</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45583</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,43%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>41210</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31862</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>52334</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65637</t>
+          <t>65983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91177</t>
+          <t>91875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53309</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43628</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64070</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35959</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55625</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35321</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53309</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>65065</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84630</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112981</t>
+          <t>113718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69177</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57903</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>68210</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58295</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>79354</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>58549</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>79856</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>41,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>69177</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57678</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>80881</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122899</t>
+          <t>123331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152229</t>
+          <t>152938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163418</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163418</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163418</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4348</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9058</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9546</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3637</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8737</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13196</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8193</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19963</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19221</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13246</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26829</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13202</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27238</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>13196</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8409</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19756</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>24317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42683</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>67609</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54097</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>79805</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>74425</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63153</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>88554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>61562</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>88099</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>21,76%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>25,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>67609</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>55151</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>81339</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124252</t>
+          <t>123148</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158861</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>96940</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>83521</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>110924</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>84237</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>70901</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>97946</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>72478</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>99287</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>24,63%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>96940</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>82862</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>111134</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161242</t>
+          <t>163088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203389</t>
+          <t>201476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>167821</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>152406</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>184746</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>159836</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>142682</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>173522</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>144258</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>175539</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>46,73%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>167821</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>151390</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>182720</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307525</t>
+          <t>305656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352295</t>
+          <t>350012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>488</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>342067</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>342067</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>342067</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
